--- a/internal_doc/05.测试设计/可靠性测试/aggregate故障测试（初稿）.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/aggregate故障测试（初稿）.xlsx
@@ -12,14 +12,111 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$26</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+需要测试协调节点</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+db.setSessionAttr({PreferedInstance:"S"
+--</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>需要指点具体是哪个备节点</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+除了网络异常其他异常都需要考虑协调节点异常</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="84">
   <si>
     <t>1、普通拥塞
 2、时间设置超过9s延迟</t>
@@ -151,10 +248,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>等友滨确认后再考虑具体测试点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>同断网，另考虑coord、catalog、dataRG组合的场景，如下：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -192,18 +285,6 @@
   </si>
   <si>
     <t>断网后组内重新选主；恢复网络后在新主查询的数据正确；断网之前没有数据更新则网络恢复后aggregate查询的数据在断网前后一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点跟其他catalog备节点网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG主节点与dataRG备节点网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord主节点与dataRG主、备节点网络单通</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -256,14 +337,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>$project/$match/$limit/$skip/$group/$sort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询过程中编目节点更新的情况（基本操作考虑（余婷））</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dataRG备节点断网</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -357,11 +430,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>故障时间最小时间7s则不触发选主，查询成功；故障超过7s后组内重新选主，恢复网络后在新主查询的数据正确；故障之前没有数据更新则网络恢复后aggregate查询的数据在断网前后一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置数据优先从被节点读取（db.setSessionAttr({PreferedInstance:"S"})）</t>
+    <t>查询过程中编目节点更新的情况（基本操作考虑（余婷））</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$project/$match/$limit/$skip/$group/$sort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord和dataRG备节点不在同一个主机，设置数据优先从被节点读取（db.setSessionAttr({PreferedInstance:"S"})）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、查询操作成功，结果返回正确；  2、查询失败，返回正确的错误提示信息；故障恢复后重新操作成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>协调节点需要测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -369,7 +454,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -425,6 +510,34 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -820,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.25" style="6" customWidth="1"/>
@@ -861,22 +974,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -895,16 +1008,16 @@
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
       <c r="D4" s="7" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="81">
@@ -912,16 +1025,16 @@
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="15" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="40.5">
@@ -929,19 +1042,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>21</v>
@@ -952,13 +1065,13 @@
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="15" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G7" s="7"/>
     </row>
@@ -967,19 +1080,19 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>0</v>
@@ -990,34 +1103,34 @@
       <c r="B9" s="7"/>
       <c r="C9" s="8"/>
       <c r="D9" s="15" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="40.5">
       <c r="A10" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -1026,13 +1139,13 @@
       <c r="B11" s="7"/>
       <c r="C11" s="8"/>
       <c r="D11" s="15" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G11" s="7"/>
     </row>
@@ -1041,16 +1154,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>13</v>
@@ -1062,19 +1175,19 @@
         <v>15</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>30</v>
@@ -1082,58 +1195,58 @@
     </row>
     <row r="14" spans="1:7" ht="67.5">
       <c r="A14" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="27">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" ht="40.5">
       <c r="A16" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -1142,19 +1255,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -1163,19 +1276,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -1184,19 +1297,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E19" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -1205,31 +1318,31 @@
         <v>4</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E20" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7" ht="67.5">
       <c r="A21" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -1250,14 +1363,14 @@
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>19</v>
@@ -1280,13 +1393,13 @@
         <v>25</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -1298,113 +1411,75 @@
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" ht="40.5">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:7" ht="67.5">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" ht="40.5">
+      <c r="A27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" ht="40.5">
+      <c r="A28" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
+      <c r="C29" s="8"/>
       <c r="D29" s="7"/>
-      <c r="E29" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
       <c r="G29" s="7"/>
     </row>
-    <row r="30" spans="1:7" ht="40.5">
-      <c r="A30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G30" s="4"/>
-    </row>
-    <row r="31" spans="1:7" ht="40.5">
-      <c r="A31" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
+    <row r="30" spans="1:7">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G29"/>
+  <autoFilter ref="A1:G26"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
